--- a/data-manipulation-scripts/sheets-cleanup/processed_sheets/REGULADOR RETIFICADOR 04_02.xlsx
+++ b/data-manipulation-scripts/sheets-cleanup/processed_sheets/REGULADOR RETIFICADOR 04_02.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E34"/>
+  <dimension ref="A1:E33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1154,7 +1154,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr"/>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>190</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -1187,37 +1191,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>7908073708577</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>RETIFICADOR CORRENTE  SMARTFOX POP100</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="n">
-        <v>33</v>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
           <t> </t>
         </is>
       </c>
-      <c r="C34" t="inlineStr"/>
-      <c r="D34" t="inlineStr"/>
-      <c r="E34" t="inlineStr"/>
+      <c r="C33" t="inlineStr"/>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data-manipulation-scripts/sheets-cleanup/processed_sheets/REGULADOR RETIFICADOR 04_02.xlsx
+++ b/data-manipulation-scripts/sheets-cleanup/processed_sheets/REGULADOR RETIFICADOR 04_02.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E33"/>
+  <dimension ref="A1:D34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -432,11 +432,6 @@
           <t>QUANTIDADE</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>PREÇO</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -457,11 +452,6 @@
           <t>3</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -482,11 +472,6 @@
           <t>3</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>225</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -507,11 +492,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>130</t>
-        </is>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -532,11 +512,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -557,11 +532,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -582,11 +552,6 @@
           <t>3</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -607,7 +572,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -628,11 +592,6 @@
           <t>3</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>105</t>
-        </is>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -653,11 +612,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>110</t>
-        </is>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -678,11 +632,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>160</t>
-        </is>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -703,11 +652,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>160</t>
-        </is>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -728,7 +672,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -749,11 +692,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -766,7 +704,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>REGULADOR  ZOUIL AN125 BUREGULADOR MAN 2006 A 2010/ YES125 2006 A 2010/ INTRUDER125 2008 A 2011</t>
+          <t>REGULADOR  ZOUIL  FAN125/ BURMAN 2006 A 2010/ YES125 2006 A 2010/ INTRUDER125 2008 A 2011</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -774,7 +712,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -795,11 +732,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>170</t>
-        </is>
-      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -820,11 +752,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>130</t>
-        </is>
-      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -845,7 +772,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -866,11 +792,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -891,11 +812,6 @@
           <t>6</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>140</t>
-        </is>
-      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -916,11 +832,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>210</t>
-        </is>
-      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -941,11 +852,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -966,11 +872,6 @@
           <t>3</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>105</t>
-        </is>
-      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -991,11 +892,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>130</t>
-        </is>
-      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -1008,7 +904,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>REGULADOR  IRON BUREGULADOR MAN125 185369</t>
+          <t>REGULADOR  IRON BURMAN125 185369</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1016,7 +912,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -1037,11 +932,6 @@
           <t>3</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>140</t>
-        </is>
-      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -1062,11 +952,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>230</t>
-        </is>
-      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -1087,7 +972,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -1108,7 +992,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -1129,11 +1012,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>130</t>
-        </is>
-      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -1154,11 +1032,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>190</t>
-        </is>
-      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -1179,24 +1052,26 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>32</v>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
+        <v>31</v>
+      </c>
+      <c r="B33" t="inlineStr"/>
       <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr"/>
-      <c r="E33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>32</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr"/>
+      <c r="D34" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
